--- a/product-definitions/spreadsheet/aerosol-backscatter-radial-winds.xlsx
+++ b/product-definitions/spreadsheet/aerosol-backscatter-radial-winds.xlsx
@@ -343,7 +343,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$£-809]#,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -359,11 +359,6 @@
       <b/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
@@ -405,7 +400,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -419,66 +414,59 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -768,7 +756,7 @@
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -785,10 +773,10 @@
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>15000.0</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -802,7 +790,7 @@
       <c r="B6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>2.0</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -912,7 +900,7 @@
       <c r="B13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>64.0</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -940,7 +928,7 @@
       <c r="B15" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="6">
         <v>1024.0</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -2372,44 +2360,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.0" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
     </row>
     <row r="2" ht="12.0" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="9">
         <v>1.0</v>
       </c>
     </row>
@@ -2417,10 +2405,10 @@
       <c r="A3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <v>1.0</v>
       </c>
     </row>
@@ -3443,723 +3431,723 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="13"/>
+      <c r="F1" s="12"/>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="15"/>
+      <c r="C2" s="13"/>
     </row>
     <row r="3">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="14" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="13" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="15"/>
+      <c r="C6" s="13"/>
       <c r="D6" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="13" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="15">
         <v>-1.0E20</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="13" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="13" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11"/>
+      <c r="A11" s="10"/>
       <c r="B11" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="16" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="19"/>
+      <c r="C13" s="17"/>
     </row>
     <row r="14">
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="13" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="14" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="14" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="16"/>
+      <c r="C17" s="14"/>
       <c r="D17" s="3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="14" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="B21" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="14" t="s">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="B22" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="23">
-      <c r="C23" s="16"/>
-    </row>
-    <row r="24">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="C23" s="14"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="19"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="14" t="s">
+      <c r="C24" s="17"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="B25" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="14" t="s">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="B26" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="14" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="B27" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="14" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="14" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="B28" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="16"/>
+      <c r="C28" s="14"/>
       <c r="D28" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="14" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="B29" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="14" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="14" t="s">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="B30" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="20">
+      <c r="C30" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="14" t="s">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="B31" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="14" t="s">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="B32" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="14" t="s">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="B33" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="34">
-      <c r="C34" s="16"/>
-    </row>
-    <row r="35">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="C34" s="14"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C35" s="19"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="14" t="s">
+      <c r="C35" s="17"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="B36" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="14" t="s">
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="B37" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="14" t="s">
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="B38" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="14" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="14" t="s">
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="B39" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C39" s="16"/>
+      <c r="C39" s="14"/>
       <c r="D39" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="14" t="s">
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="B40" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="14" t="s">
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="B41" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="14" t="s">
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="B42" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="14" t="s">
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="B43" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="14" t="s">
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="B44" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="45">
-      <c r="C45" s="16"/>
-    </row>
-    <row r="46">
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="C45" s="14"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C46" s="19"/>
-    </row>
-    <row r="47">
-      <c r="B47" s="14" t="s">
+      <c r="C46" s="17"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="B47" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="14" t="s">
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="B48" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="14" t="s">
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="B49" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="14" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="14" t="s">
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="B50" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="16"/>
+      <c r="C50" s="14"/>
       <c r="D50" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="14" t="s">
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="B51" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="14" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="14" t="s">
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="B52" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C52" s="20">
+      <c r="C52" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="14" t="s">
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="B53" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="14" t="s">
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="B54" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="14" t="s">
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="B55" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C55" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="56">
-      <c r="C56" s="16"/>
-    </row>
-    <row r="57">
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="C56" s="14"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C57" s="19"/>
-    </row>
-    <row r="58">
-      <c r="B58" s="14" t="s">
+      <c r="C57" s="17"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="B58" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C58" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="14" t="s">
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="B59" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C59" s="21" t="s">
+      <c r="C59" s="19" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="14" t="s">
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="B60" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="C60" s="14" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="14" t="s">
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="B61" s="3" t="s">
         <v>66</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="14" t="s">
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="B62" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="14" t="s">
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="B63" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C63" s="20">
+      <c r="C63" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="14" t="s">
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="B64" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="C64" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="14" t="s">
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="B65" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C65" s="15" t="s">
+      <c r="C65" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="14" t="s">
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="B66" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="14" t="s">
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="B67" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C67" s="16" t="s">
+      <c r="C67" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="68">
-      <c r="C68" s="19"/>
-    </row>
-    <row r="69">
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="C68" s="17"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C69" s="19"/>
-    </row>
-    <row r="70">
-      <c r="B70" s="14" t="s">
+      <c r="C69" s="17"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="B70" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C70" s="15" t="s">
+      <c r="C70" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="14" t="s">
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="B71" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C71" s="16" t="s">
+      <c r="C71" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="14" t="s">
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="B72" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C72" s="16" t="s">
+      <c r="C72" s="14" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="14" t="s">
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="B73" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="14" t="s">
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="B74" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C74" s="16" t="s">
+      <c r="C74" s="14" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="14" t="s">
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="B75" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C75" s="20">
+      <c r="C75" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="14" t="s">
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="B76" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="C76" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="14" t="s">
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="B77" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C77" s="15" t="s">
+      <c r="C77" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="14" t="s">
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="B78" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C78" s="16" t="s">
+      <c r="C78" s="14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" s="14" t="s">
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="B79" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C79" s="16" t="s">
+      <c r="C79" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="80">
-      <c r="C80" s="16"/>
-    </row>
-    <row r="81">
-      <c r="C81" s="16"/>
-    </row>
-    <row r="82">
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="C80" s="14"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="C81" s="14"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C82" s="19"/>
-    </row>
-    <row r="83">
-      <c r="B83" s="14" t="s">
+      <c r="C82" s="17"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="B83" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C83" s="15" t="s">
+      <c r="C83" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="14" t="s">
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="B84" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C84" s="16" t="s">
+      <c r="C84" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" s="14" t="s">
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="B85" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C85" s="16">
+      <c r="C85" s="14">
         <v>1.0</v>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="14" t="s">
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="B86" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="14" t="s">
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="B87" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="14" t="s">
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="B88" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C88" s="20">
+      <c r="C88" s="18">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="14" t="s">
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="B89" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C89" s="15" t="s">
+      <c r="C89" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="14" t="s">
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="B90" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C90" s="15" t="s">
+      <c r="C90" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="14" t="s">
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="B91" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C91" s="16" t="s">
+      <c r="C91" s="14" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" s="14" t="s">
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="B92" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C92" s="16" t="s">
+      <c r="C92" s="14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="93">
-      <c r="C93" s="16"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="22" t="s">
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="C93" s="14"/>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="20" t="s">
         <v>95</v>
       </c>
       <c r="B94" s="5"/>
-      <c r="C94" s="23"/>
+      <c r="C94" s="21"/>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="5"/>
       <c r="B95" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C95" s="23" t="s">
+      <c r="C95" s="21" t="s">
         <v>96</v>
       </c>
       <c r="D95" s="5"/>
@@ -4167,25 +4155,25 @@
       <c r="F95" s="5"/>
       <c r="G95" s="5"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="5"/>
-      <c r="B96" s="24" t="s">
+      <c r="B96" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C96" s="18" t="s">
+      <c r="C96" s="16" t="s">
         <v>64</v>
       </c>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
-      <c r="F96" s="22"/>
+      <c r="F96" s="20"/>
       <c r="G96" s="5"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="5"/>
       <c r="B97" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C97" s="25">
+      <c r="C97" s="22">
         <v>1.0</v>
       </c>
       <c r="D97" s="5"/>
@@ -4193,23 +4181,23 @@
       <c r="F97" s="5"/>
       <c r="G97" s="5"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="5"/>
       <c r="B98" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C98" s="23"/>
+      <c r="C98" s="21"/>
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="5"/>
       <c r="B99" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C99" s="18" t="s">
+      <c r="C99" s="16" t="s">
         <v>97</v>
       </c>
       <c r="D99" s="5"/>
@@ -4217,12 +4205,12 @@
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="5"/>
       <c r="B100" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C100" s="18" t="s">
+      <c r="C100" s="16" t="s">
         <v>99</v>
       </c>
       <c r="D100" s="5"/>
@@ -4230,12 +4218,12 @@
       <c r="F100" s="5"/>
       <c r="G100" s="5"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="5"/>
-      <c r="B101" s="23" t="s">
+      <c r="B101" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="26" t="s">
+      <c r="C101" s="23" t="s">
         <v>101</v>
       </c>
       <c r="D101" s="5"/>
@@ -4243,7 +4231,7 @@
       <c r="F101" s="5"/>
       <c r="G101" s="5"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -4252,23 +4240,23 @@
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
     </row>
-    <row r="103">
-      <c r="A103" s="22" t="s">
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="20" t="s">
         <v>102</v>
       </c>
       <c r="B103" s="5"/>
-      <c r="C103" s="23"/>
+      <c r="C103" s="21"/>
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="5"/>
       <c r="B104" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C104" s="23" t="s">
+      <c r="C104" s="21" t="s">
         <v>96</v>
       </c>
       <c r="D104" s="5"/>
@@ -4276,25 +4264,25 @@
       <c r="F104" s="5"/>
       <c r="G104" s="5"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="5"/>
-      <c r="B105" s="24" t="s">
+      <c r="B105" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C105" s="18" t="s">
+      <c r="C105" s="16" t="s">
         <v>64</v>
       </c>
       <c r="D105" s="5"/>
       <c r="E105" s="5"/>
-      <c r="F105" s="22"/>
+      <c r="F105" s="20"/>
       <c r="G105" s="5"/>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="5"/>
       <c r="B106" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C106" s="25">
+      <c r="C106" s="22">
         <v>1.0</v>
       </c>
       <c r="D106" s="5"/>
@@ -4302,23 +4290,23 @@
       <c r="F106" s="5"/>
       <c r="G106" s="5"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="5"/>
       <c r="B107" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C107" s="23"/>
+      <c r="C107" s="21"/>
       <c r="D107" s="5"/>
       <c r="E107" s="5"/>
       <c r="F107" s="5"/>
       <c r="G107" s="5"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="5"/>
       <c r="B108" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C108" s="18" t="s">
+      <c r="C108" s="16" t="s">
         <v>103</v>
       </c>
       <c r="D108" s="5"/>
@@ -4326,12 +4314,12 @@
       <c r="F108" s="5"/>
       <c r="G108" s="5"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="5"/>
       <c r="B109" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C109" s="18" t="s">
+      <c r="C109" s="16" t="s">
         <v>99</v>
       </c>
       <c r="D109" s="5"/>
@@ -4339,12 +4327,12 @@
       <c r="F109" s="5"/>
       <c r="G109" s="5"/>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="5"/>
-      <c r="B110" s="23" t="s">
+      <c r="B110" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="C110" s="26" t="s">
+      <c r="C110" s="23" t="s">
         <v>101</v>
       </c>
       <c r="D110" s="5"/>
@@ -4353,604 +4341,604 @@
       <c r="G110" s="5"/>
     </row>
     <row r="111" ht="12.0" customHeight="1">
-      <c r="C111" s="19"/>
+      <c r="C111" s="17"/>
     </row>
     <row r="112" ht="12.0" customHeight="1">
-      <c r="C112" s="19"/>
+      <c r="C112" s="17"/>
     </row>
     <row r="113" ht="12.0" customHeight="1">
-      <c r="C113" s="19"/>
+      <c r="C113" s="17"/>
     </row>
     <row r="114" ht="12.0" customHeight="1">
-      <c r="C114" s="19"/>
+      <c r="C114" s="17"/>
     </row>
     <row r="115" ht="12.0" customHeight="1">
-      <c r="C115" s="19"/>
+      <c r="C115" s="17"/>
     </row>
     <row r="116" ht="12.0" customHeight="1">
-      <c r="C116" s="19"/>
+      <c r="C116" s="17"/>
     </row>
     <row r="117" ht="12.0" customHeight="1">
-      <c r="C117" s="19"/>
+      <c r="C117" s="17"/>
     </row>
     <row r="118" ht="12.0" customHeight="1">
-      <c r="C118" s="19"/>
+      <c r="C118" s="17"/>
     </row>
     <row r="119" ht="12.0" customHeight="1">
-      <c r="C119" s="19"/>
+      <c r="C119" s="17"/>
     </row>
     <row r="120" ht="12.0" customHeight="1">
-      <c r="C120" s="19"/>
+      <c r="C120" s="17"/>
     </row>
     <row r="121" ht="12.0" customHeight="1">
-      <c r="C121" s="19"/>
+      <c r="C121" s="17"/>
     </row>
     <row r="122" ht="12.0" customHeight="1">
-      <c r="C122" s="19"/>
+      <c r="C122" s="17"/>
     </row>
     <row r="123" ht="12.0" customHeight="1">
-      <c r="C123" s="19"/>
+      <c r="C123" s="17"/>
     </row>
     <row r="124" ht="12.0" customHeight="1">
-      <c r="C124" s="19"/>
+      <c r="C124" s="17"/>
     </row>
     <row r="125" ht="12.0" customHeight="1">
-      <c r="C125" s="19"/>
+      <c r="C125" s="17"/>
     </row>
     <row r="126" ht="12.0" customHeight="1">
-      <c r="C126" s="19"/>
+      <c r="C126" s="17"/>
     </row>
     <row r="127" ht="12.0" customHeight="1">
-      <c r="C127" s="19"/>
+      <c r="C127" s="17"/>
     </row>
     <row r="128" ht="12.0" customHeight="1">
-      <c r="C128" s="19"/>
+      <c r="C128" s="17"/>
     </row>
     <row r="129" ht="12.0" customHeight="1">
-      <c r="C129" s="19"/>
+      <c r="C129" s="17"/>
     </row>
     <row r="130" ht="12.0" customHeight="1">
-      <c r="C130" s="19"/>
+      <c r="C130" s="17"/>
     </row>
     <row r="131" ht="12.0" customHeight="1">
-      <c r="C131" s="19"/>
+      <c r="C131" s="17"/>
     </row>
     <row r="132" ht="12.0" customHeight="1">
-      <c r="C132" s="19"/>
+      <c r="C132" s="17"/>
     </row>
     <row r="133" ht="12.0" customHeight="1">
-      <c r="C133" s="19"/>
+      <c r="C133" s="17"/>
     </row>
     <row r="134" ht="12.0" customHeight="1">
-      <c r="C134" s="19"/>
+      <c r="C134" s="17"/>
     </row>
     <row r="135" ht="12.0" customHeight="1">
-      <c r="C135" s="19"/>
+      <c r="C135" s="17"/>
     </row>
     <row r="136" ht="12.0" customHeight="1">
-      <c r="C136" s="19"/>
+      <c r="C136" s="17"/>
     </row>
     <row r="137" ht="12.0" customHeight="1">
-      <c r="C137" s="19"/>
+      <c r="C137" s="17"/>
     </row>
     <row r="138" ht="12.0" customHeight="1">
-      <c r="C138" s="19"/>
+      <c r="C138" s="17"/>
     </row>
     <row r="139" ht="12.0" customHeight="1">
-      <c r="C139" s="19"/>
+      <c r="C139" s="17"/>
     </row>
     <row r="140" ht="12.0" customHeight="1">
-      <c r="C140" s="19"/>
+      <c r="C140" s="17"/>
     </row>
     <row r="141" ht="12.0" customHeight="1">
-      <c r="C141" s="19"/>
+      <c r="C141" s="17"/>
     </row>
     <row r="142" ht="12.0" customHeight="1">
-      <c r="C142" s="19"/>
+      <c r="C142" s="17"/>
     </row>
     <row r="143" ht="12.0" customHeight="1">
-      <c r="C143" s="19"/>
+      <c r="C143" s="17"/>
     </row>
     <row r="144" ht="12.0" customHeight="1">
-      <c r="C144" s="19"/>
+      <c r="C144" s="17"/>
     </row>
     <row r="145" ht="12.0" customHeight="1">
-      <c r="C145" s="19"/>
+      <c r="C145" s="17"/>
     </row>
     <row r="146" ht="12.0" customHeight="1">
-      <c r="C146" s="19"/>
+      <c r="C146" s="17"/>
     </row>
     <row r="147" ht="12.0" customHeight="1">
-      <c r="C147" s="19"/>
+      <c r="C147" s="17"/>
     </row>
     <row r="148" ht="12.0" customHeight="1">
-      <c r="C148" s="19"/>
+      <c r="C148" s="17"/>
     </row>
     <row r="149" ht="12.0" customHeight="1">
-      <c r="C149" s="19"/>
+      <c r="C149" s="17"/>
     </row>
     <row r="150" ht="12.0" customHeight="1">
-      <c r="C150" s="19"/>
+      <c r="C150" s="17"/>
     </row>
     <row r="151" ht="12.0" customHeight="1">
-      <c r="C151" s="19"/>
+      <c r="C151" s="17"/>
     </row>
     <row r="152" ht="12.0" customHeight="1">
-      <c r="C152" s="19"/>
+      <c r="C152" s="17"/>
     </row>
     <row r="153" ht="12.0" customHeight="1">
-      <c r="C153" s="19"/>
+      <c r="C153" s="17"/>
     </row>
     <row r="154" ht="12.0" customHeight="1">
-      <c r="C154" s="19"/>
+      <c r="C154" s="17"/>
     </row>
     <row r="155" ht="12.0" customHeight="1">
-      <c r="C155" s="19"/>
+      <c r="C155" s="17"/>
     </row>
     <row r="156" ht="12.0" customHeight="1">
-      <c r="C156" s="19"/>
+      <c r="C156" s="17"/>
     </row>
     <row r="157" ht="12.0" customHeight="1">
-      <c r="C157" s="19"/>
+      <c r="C157" s="17"/>
     </row>
     <row r="158" ht="12.0" customHeight="1">
-      <c r="C158" s="19"/>
+      <c r="C158" s="17"/>
     </row>
     <row r="159" ht="12.0" customHeight="1">
-      <c r="C159" s="19"/>
+      <c r="C159" s="17"/>
     </row>
     <row r="160" ht="12.0" customHeight="1">
-      <c r="C160" s="19"/>
+      <c r="C160" s="17"/>
     </row>
     <row r="161" ht="12.0" customHeight="1">
-      <c r="C161" s="19"/>
+      <c r="C161" s="17"/>
     </row>
     <row r="162" ht="12.0" customHeight="1">
-      <c r="C162" s="19"/>
+      <c r="C162" s="17"/>
     </row>
     <row r="163" ht="12.0" customHeight="1">
-      <c r="C163" s="19"/>
+      <c r="C163" s="17"/>
     </row>
     <row r="164" ht="12.0" customHeight="1">
-      <c r="C164" s="19"/>
+      <c r="C164" s="17"/>
     </row>
     <row r="165" ht="12.0" customHeight="1">
-      <c r="C165" s="19"/>
+      <c r="C165" s="17"/>
     </row>
     <row r="166" ht="12.0" customHeight="1">
-      <c r="C166" s="19"/>
+      <c r="C166" s="17"/>
     </row>
     <row r="167" ht="12.0" customHeight="1">
-      <c r="C167" s="19"/>
+      <c r="C167" s="17"/>
     </row>
     <row r="168" ht="12.0" customHeight="1">
-      <c r="C168" s="19"/>
+      <c r="C168" s="17"/>
     </row>
     <row r="169" ht="12.0" customHeight="1">
-      <c r="C169" s="19"/>
+      <c r="C169" s="17"/>
     </row>
     <row r="170" ht="12.0" customHeight="1">
-      <c r="C170" s="19"/>
+      <c r="C170" s="17"/>
     </row>
     <row r="171" ht="12.0" customHeight="1">
-      <c r="C171" s="19"/>
+      <c r="C171" s="17"/>
     </row>
     <row r="172" ht="12.0" customHeight="1">
-      <c r="C172" s="19"/>
+      <c r="C172" s="17"/>
     </row>
     <row r="173" ht="12.0" customHeight="1">
-      <c r="C173" s="19"/>
+      <c r="C173" s="17"/>
     </row>
     <row r="174" ht="12.0" customHeight="1">
-      <c r="C174" s="19"/>
+      <c r="C174" s="17"/>
     </row>
     <row r="175" ht="12.0" customHeight="1">
-      <c r="C175" s="19"/>
+      <c r="C175" s="17"/>
     </row>
     <row r="176" ht="12.0" customHeight="1">
-      <c r="C176" s="19"/>
+      <c r="C176" s="17"/>
     </row>
     <row r="177" ht="12.0" customHeight="1">
-      <c r="C177" s="19"/>
+      <c r="C177" s="17"/>
     </row>
     <row r="178" ht="12.0" customHeight="1">
-      <c r="C178" s="19"/>
+      <c r="C178" s="17"/>
     </row>
     <row r="179" ht="12.0" customHeight="1">
-      <c r="C179" s="19"/>
+      <c r="C179" s="17"/>
     </row>
     <row r="180" ht="12.0" customHeight="1">
-      <c r="C180" s="19"/>
+      <c r="C180" s="17"/>
     </row>
     <row r="181" ht="12.0" customHeight="1">
-      <c r="C181" s="19"/>
+      <c r="C181" s="17"/>
     </row>
     <row r="182" ht="12.0" customHeight="1">
-      <c r="C182" s="19"/>
+      <c r="C182" s="17"/>
     </row>
     <row r="183" ht="12.0" customHeight="1">
-      <c r="C183" s="19"/>
+      <c r="C183" s="17"/>
     </row>
     <row r="184" ht="12.0" customHeight="1">
-      <c r="C184" s="19"/>
+      <c r="C184" s="17"/>
     </row>
     <row r="185" ht="12.0" customHeight="1">
-      <c r="C185" s="19"/>
+      <c r="C185" s="17"/>
     </row>
     <row r="186" ht="12.0" customHeight="1">
-      <c r="C186" s="19"/>
+      <c r="C186" s="17"/>
     </row>
     <row r="187" ht="12.0" customHeight="1">
-      <c r="C187" s="19"/>
+      <c r="C187" s="17"/>
     </row>
     <row r="188" ht="12.0" customHeight="1">
-      <c r="C188" s="19"/>
+      <c r="C188" s="17"/>
     </row>
     <row r="189" ht="12.0" customHeight="1">
-      <c r="C189" s="19"/>
+      <c r="C189" s="17"/>
     </row>
     <row r="190" ht="12.0" customHeight="1">
-      <c r="C190" s="19"/>
+      <c r="C190" s="17"/>
     </row>
     <row r="191" ht="12.0" customHeight="1">
-      <c r="C191" s="19"/>
+      <c r="C191" s="17"/>
     </row>
     <row r="192" ht="12.0" customHeight="1">
-      <c r="C192" s="19"/>
+      <c r="C192" s="17"/>
     </row>
     <row r="193" ht="12.0" customHeight="1">
-      <c r="C193" s="19"/>
+      <c r="C193" s="17"/>
     </row>
     <row r="194" ht="12.0" customHeight="1">
-      <c r="C194" s="19"/>
+      <c r="C194" s="17"/>
     </row>
     <row r="195" ht="12.0" customHeight="1">
-      <c r="C195" s="19"/>
+      <c r="C195" s="17"/>
     </row>
     <row r="196" ht="12.0" customHeight="1">
-      <c r="C196" s="19"/>
+      <c r="C196" s="17"/>
     </row>
     <row r="197" ht="12.0" customHeight="1">
-      <c r="C197" s="19"/>
+      <c r="C197" s="17"/>
     </row>
     <row r="198" ht="12.0" customHeight="1">
-      <c r="C198" s="19"/>
+      <c r="C198" s="17"/>
     </row>
     <row r="199" ht="12.0" customHeight="1">
-      <c r="C199" s="19"/>
+      <c r="C199" s="17"/>
     </row>
     <row r="200" ht="12.0" customHeight="1">
-      <c r="C200" s="19"/>
+      <c r="C200" s="17"/>
     </row>
     <row r="201" ht="12.0" customHeight="1">
-      <c r="C201" s="19"/>
+      <c r="C201" s="17"/>
     </row>
     <row r="202" ht="12.0" customHeight="1">
-      <c r="C202" s="19"/>
+      <c r="C202" s="17"/>
     </row>
     <row r="203" ht="12.0" customHeight="1">
-      <c r="C203" s="19"/>
+      <c r="C203" s="17"/>
     </row>
     <row r="204" ht="12.0" customHeight="1">
-      <c r="C204" s="19"/>
+      <c r="C204" s="17"/>
     </row>
     <row r="205" ht="12.0" customHeight="1">
-      <c r="C205" s="19"/>
+      <c r="C205" s="17"/>
     </row>
     <row r="206" ht="12.0" customHeight="1">
-      <c r="C206" s="19"/>
+      <c r="C206" s="17"/>
     </row>
     <row r="207" ht="12.0" customHeight="1">
-      <c r="C207" s="19"/>
+      <c r="C207" s="17"/>
     </row>
     <row r="208" ht="12.0" customHeight="1">
-      <c r="C208" s="19"/>
+      <c r="C208" s="17"/>
     </row>
     <row r="209" ht="12.0" customHeight="1">
-      <c r="C209" s="19"/>
+      <c r="C209" s="17"/>
     </row>
     <row r="210" ht="12.0" customHeight="1">
-      <c r="C210" s="19"/>
+      <c r="C210" s="17"/>
     </row>
     <row r="211" ht="12.0" customHeight="1">
-      <c r="C211" s="19"/>
+      <c r="C211" s="17"/>
     </row>
     <row r="212" ht="12.0" customHeight="1">
-      <c r="C212" s="19"/>
+      <c r="C212" s="17"/>
     </row>
     <row r="213" ht="12.0" customHeight="1">
-      <c r="C213" s="19"/>
+      <c r="C213" s="17"/>
     </row>
     <row r="214" ht="12.0" customHeight="1">
-      <c r="C214" s="19"/>
+      <c r="C214" s="17"/>
     </row>
     <row r="215" ht="12.0" customHeight="1">
-      <c r="C215" s="19"/>
+      <c r="C215" s="17"/>
     </row>
     <row r="216" ht="12.0" customHeight="1">
-      <c r="C216" s="19"/>
+      <c r="C216" s="17"/>
     </row>
     <row r="217" ht="12.0" customHeight="1">
-      <c r="C217" s="19"/>
+      <c r="C217" s="17"/>
     </row>
     <row r="218" ht="12.0" customHeight="1">
-      <c r="C218" s="19"/>
+      <c r="C218" s="17"/>
     </row>
     <row r="219" ht="12.0" customHeight="1">
-      <c r="C219" s="19"/>
+      <c r="C219" s="17"/>
     </row>
     <row r="220" ht="12.0" customHeight="1">
-      <c r="C220" s="19"/>
+      <c r="C220" s="17"/>
     </row>
     <row r="221" ht="12.0" customHeight="1">
-      <c r="C221" s="19"/>
+      <c r="C221" s="17"/>
     </row>
     <row r="222" ht="12.0" customHeight="1">
-      <c r="C222" s="19"/>
+      <c r="C222" s="17"/>
     </row>
     <row r="223" ht="12.0" customHeight="1">
-      <c r="C223" s="19"/>
+      <c r="C223" s="17"/>
     </row>
     <row r="224" ht="12.0" customHeight="1">
-      <c r="C224" s="19"/>
+      <c r="C224" s="17"/>
     </row>
     <row r="225" ht="12.0" customHeight="1">
-      <c r="C225" s="19"/>
+      <c r="C225" s="17"/>
     </row>
     <row r="226" ht="12.0" customHeight="1">
-      <c r="C226" s="19"/>
+      <c r="C226" s="17"/>
     </row>
     <row r="227" ht="12.0" customHeight="1">
-      <c r="C227" s="19"/>
+      <c r="C227" s="17"/>
     </row>
     <row r="228" ht="12.0" customHeight="1">
-      <c r="C228" s="19"/>
+      <c r="C228" s="17"/>
     </row>
     <row r="229" ht="12.0" customHeight="1">
-      <c r="C229" s="19"/>
+      <c r="C229" s="17"/>
     </row>
     <row r="230" ht="12.0" customHeight="1">
-      <c r="C230" s="19"/>
+      <c r="C230" s="17"/>
     </row>
     <row r="231" ht="12.0" customHeight="1">
-      <c r="C231" s="19"/>
+      <c r="C231" s="17"/>
     </row>
     <row r="232" ht="12.0" customHeight="1">
-      <c r="C232" s="19"/>
+      <c r="C232" s="17"/>
     </row>
     <row r="233" ht="12.0" customHeight="1">
-      <c r="C233" s="19"/>
+      <c r="C233" s="17"/>
     </row>
     <row r="234" ht="12.0" customHeight="1">
-      <c r="C234" s="19"/>
+      <c r="C234" s="17"/>
     </row>
     <row r="235" ht="12.0" customHeight="1">
-      <c r="C235" s="19"/>
+      <c r="C235" s="17"/>
     </row>
     <row r="236" ht="12.0" customHeight="1">
-      <c r="C236" s="19"/>
+      <c r="C236" s="17"/>
     </row>
     <row r="237" ht="12.0" customHeight="1">
-      <c r="C237" s="19"/>
+      <c r="C237" s="17"/>
     </row>
     <row r="238" ht="12.0" customHeight="1">
-      <c r="C238" s="19"/>
+      <c r="C238" s="17"/>
     </row>
     <row r="239" ht="12.0" customHeight="1">
-      <c r="C239" s="19"/>
+      <c r="C239" s="17"/>
     </row>
     <row r="240" ht="12.0" customHeight="1">
-      <c r="C240" s="19"/>
+      <c r="C240" s="17"/>
     </row>
     <row r="241" ht="12.0" customHeight="1">
-      <c r="C241" s="19"/>
+      <c r="C241" s="17"/>
     </row>
     <row r="242" ht="12.0" customHeight="1">
-      <c r="C242" s="19"/>
+      <c r="C242" s="17"/>
     </row>
     <row r="243" ht="12.0" customHeight="1">
-      <c r="C243" s="19"/>
+      <c r="C243" s="17"/>
     </row>
     <row r="244" ht="12.0" customHeight="1">
-      <c r="C244" s="19"/>
+      <c r="C244" s="17"/>
     </row>
     <row r="245" ht="12.0" customHeight="1">
-      <c r="C245" s="19"/>
+      <c r="C245" s="17"/>
     </row>
     <row r="246" ht="12.0" customHeight="1">
-      <c r="C246" s="19"/>
+      <c r="C246" s="17"/>
     </row>
     <row r="247" ht="12.0" customHeight="1">
-      <c r="C247" s="19"/>
+      <c r="C247" s="17"/>
     </row>
     <row r="248" ht="12.0" customHeight="1">
-      <c r="C248" s="19"/>
+      <c r="C248" s="17"/>
     </row>
     <row r="249" ht="12.0" customHeight="1">
-      <c r="C249" s="19"/>
+      <c r="C249" s="17"/>
     </row>
     <row r="250" ht="12.0" customHeight="1">
-      <c r="C250" s="19"/>
+      <c r="C250" s="17"/>
     </row>
     <row r="251" ht="12.0" customHeight="1">
-      <c r="C251" s="19"/>
+      <c r="C251" s="17"/>
     </row>
     <row r="252" ht="12.0" customHeight="1">
-      <c r="C252" s="19"/>
+      <c r="C252" s="17"/>
     </row>
     <row r="253" ht="12.0" customHeight="1">
-      <c r="C253" s="19"/>
+      <c r="C253" s="17"/>
     </row>
     <row r="254" ht="12.0" customHeight="1">
-      <c r="C254" s="19"/>
+      <c r="C254" s="17"/>
     </row>
     <row r="255" ht="12.0" customHeight="1">
-      <c r="C255" s="19"/>
+      <c r="C255" s="17"/>
     </row>
     <row r="256" ht="12.0" customHeight="1">
-      <c r="C256" s="19"/>
+      <c r="C256" s="17"/>
     </row>
     <row r="257" ht="12.0" customHeight="1">
-      <c r="C257" s="19"/>
+      <c r="C257" s="17"/>
     </row>
     <row r="258" ht="12.0" customHeight="1">
-      <c r="C258" s="19"/>
+      <c r="C258" s="17"/>
     </row>
     <row r="259" ht="12.0" customHeight="1">
-      <c r="C259" s="19"/>
+      <c r="C259" s="17"/>
     </row>
     <row r="260" ht="12.0" customHeight="1">
-      <c r="C260" s="19"/>
+      <c r="C260" s="17"/>
     </row>
     <row r="261" ht="12.0" customHeight="1">
-      <c r="C261" s="19"/>
+      <c r="C261" s="17"/>
     </row>
     <row r="262" ht="12.0" customHeight="1">
-      <c r="C262" s="19"/>
+      <c r="C262" s="17"/>
     </row>
     <row r="263" ht="12.0" customHeight="1">
-      <c r="C263" s="19"/>
+      <c r="C263" s="17"/>
     </row>
     <row r="264" ht="12.0" customHeight="1">
-      <c r="C264" s="19"/>
+      <c r="C264" s="17"/>
     </row>
     <row r="265" ht="12.0" customHeight="1">
-      <c r="C265" s="19"/>
+      <c r="C265" s="17"/>
     </row>
     <row r="266" ht="12.0" customHeight="1">
-      <c r="C266" s="19"/>
+      <c r="C266" s="17"/>
     </row>
     <row r="267" ht="12.0" customHeight="1">
-      <c r="C267" s="19"/>
+      <c r="C267" s="17"/>
     </row>
     <row r="268" ht="12.0" customHeight="1">
-      <c r="C268" s="19"/>
+      <c r="C268" s="17"/>
     </row>
     <row r="269" ht="12.0" customHeight="1">
-      <c r="C269" s="19"/>
+      <c r="C269" s="17"/>
     </row>
     <row r="270" ht="12.0" customHeight="1">
-      <c r="C270" s="19"/>
+      <c r="C270" s="17"/>
     </row>
     <row r="271" ht="12.0" customHeight="1">
-      <c r="C271" s="19"/>
+      <c r="C271" s="17"/>
     </row>
     <row r="272" ht="12.0" customHeight="1">
-      <c r="C272" s="19"/>
+      <c r="C272" s="17"/>
     </row>
     <row r="273" ht="12.0" customHeight="1">
-      <c r="C273" s="19"/>
+      <c r="C273" s="17"/>
     </row>
     <row r="274" ht="12.0" customHeight="1">
-      <c r="C274" s="19"/>
+      <c r="C274" s="17"/>
     </row>
     <row r="275" ht="12.0" customHeight="1">
-      <c r="C275" s="19"/>
+      <c r="C275" s="17"/>
     </row>
     <row r="276" ht="12.0" customHeight="1">
-      <c r="C276" s="19"/>
+      <c r="C276" s="17"/>
     </row>
     <row r="277" ht="12.0" customHeight="1">
-      <c r="C277" s="19"/>
+      <c r="C277" s="17"/>
     </row>
     <row r="278" ht="12.0" customHeight="1">
-      <c r="C278" s="19"/>
+      <c r="C278" s="17"/>
     </row>
     <row r="279" ht="12.0" customHeight="1">
-      <c r="C279" s="19"/>
+      <c r="C279" s="17"/>
     </row>
     <row r="280" ht="12.0" customHeight="1">
-      <c r="C280" s="19"/>
+      <c r="C280" s="17"/>
     </row>
     <row r="281" ht="12.0" customHeight="1">
-      <c r="C281" s="19"/>
+      <c r="C281" s="17"/>
     </row>
     <row r="282" ht="12.0" customHeight="1">
-      <c r="C282" s="19"/>
+      <c r="C282" s="17"/>
     </row>
     <row r="283" ht="12.0" customHeight="1">
-      <c r="C283" s="19"/>
+      <c r="C283" s="17"/>
     </row>
     <row r="284" ht="12.0" customHeight="1">
-      <c r="C284" s="19"/>
+      <c r="C284" s="17"/>
     </row>
     <row r="285" ht="12.0" customHeight="1">
-      <c r="C285" s="19"/>
+      <c r="C285" s="17"/>
     </row>
     <row r="286" ht="12.0" customHeight="1">
-      <c r="C286" s="19"/>
+      <c r="C286" s="17"/>
     </row>
     <row r="287" ht="12.0" customHeight="1">
-      <c r="C287" s="19"/>
+      <c r="C287" s="17"/>
     </row>
     <row r="288" ht="12.0" customHeight="1">
-      <c r="C288" s="19"/>
+      <c r="C288" s="17"/>
     </row>
     <row r="289" ht="12.0" customHeight="1">
-      <c r="C289" s="19"/>
+      <c r="C289" s="17"/>
     </row>
     <row r="290" ht="12.0" customHeight="1">
-      <c r="C290" s="19"/>
+      <c r="C290" s="17"/>
     </row>
     <row r="291" ht="12.0" customHeight="1">
-      <c r="C291" s="19"/>
+      <c r="C291" s="17"/>
     </row>
     <row r="292" ht="12.0" customHeight="1">
-      <c r="C292" s="19"/>
+      <c r="C292" s="17"/>
     </row>
     <row r="293" ht="12.0" customHeight="1">
-      <c r="C293" s="19"/>
+      <c r="C293" s="17"/>
     </row>
     <row r="294" ht="12.0" customHeight="1">
-      <c r="C294" s="19"/>
+      <c r="C294" s="17"/>
     </row>
     <row r="295" ht="12.0" customHeight="1">
-      <c r="C295" s="19"/>
+      <c r="C295" s="17"/>
     </row>
     <row r="296" ht="12.0" customHeight="1">
-      <c r="C296" s="19"/>
+      <c r="C296" s="17"/>
     </row>
     <row r="297" ht="12.0" customHeight="1">
-      <c r="C297" s="19"/>
+      <c r="C297" s="17"/>
     </row>
     <row r="298" ht="12.0" customHeight="1">
-      <c r="C298" s="19"/>
+      <c r="C298" s="17"/>
     </row>
     <row r="299" ht="12.0" customHeight="1">
-      <c r="C299" s="19"/>
+      <c r="C299" s="17"/>
     </row>
     <row r="300" ht="12.0" customHeight="1">
-      <c r="C300" s="19"/>
+      <c r="C300" s="17"/>
     </row>
     <row r="301" ht="12.0" customHeight="1">
-      <c r="C301" s="19"/>
+      <c r="C301" s="17"/>
     </row>
     <row r="302" ht="12.0" customHeight="1">
-      <c r="C302" s="19"/>
+      <c r="C302" s="17"/>
     </row>
     <row r="303" ht="12.0" customHeight="1">
-      <c r="C303" s="19"/>
+      <c r="C303" s="17"/>
     </row>
     <row r="304" ht="12.0" customHeight="1">
-      <c r="C304" s="19"/>
+      <c r="C304" s="17"/>
     </row>
     <row r="305" ht="12.0" customHeight="1">
-      <c r="C305" s="19"/>
+      <c r="C305" s="17"/>
     </row>
     <row r="306" ht="12.0" customHeight="1">
-      <c r="C306" s="19"/>
+      <c r="C306" s="17"/>
     </row>
     <row r="307" ht="12.0" customHeight="1">
-      <c r="C307" s="19"/>
+      <c r="C307" s="17"/>
     </row>
     <row r="308" ht="12.0" customHeight="1">
-      <c r="C308" s="19"/>
+      <c r="C308" s="17"/>
     </row>
     <row r="309" ht="12.0" customHeight="1">
-      <c r="C309" s="19"/>
+      <c r="C309" s="17"/>
     </row>
     <row r="310" ht="12.0" customHeight="1">
-      <c r="C310" s="19"/>
+      <c r="C310" s="17"/>
     </row>
     <row r="311" ht="15.75" customHeight="1"/>
     <row r="312" ht="15.75" customHeight="1"/>
